--- a/entrega-2/03-seleccion-regresion.xlsx
+++ b/entrega-2/03-seleccion-regresion.xlsx
@@ -1889,19 +1889,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>Incluido</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>Excluido</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr"/>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>módulo que V2 toca: Registro (V2 suma gasto compartido, aviso de guardado y confirmación de borrado)</t>
+          <t>prioridad Baja en el módulo Registro, que V2 toca: ninguna otra regla la incluye (no es Alta, no confirma un defecto y no falló en V1); conserva el resultado de la ejecución de V1</t>
         </is>
       </c>
     </row>
@@ -2030,19 +2026,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>Incluido</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Excluido</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr"/>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>módulo que V2 toca: Registro (V2 suma gasto compartido, aviso de guardado y confirmación de borrado)</t>
+          <t>prioridad Baja en el módulo Registro, que V2 toca: ninguna otra regla la incluye (no es Alta, no confirma un defecto y no falló en V1); conserva el resultado de la ejecución de V1</t>
         </is>
       </c>
     </row>
@@ -2077,19 +2069,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>Incluido</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>Excluido</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr"/>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>módulo que V2 toca: Registro (V2 suma gasto compartido, aviso de guardado y confirmación de borrado)</t>
+          <t>prioridad Baja en el módulo Registro, que V2 toca: ninguna otra regla la incluye (no es Alta, no confirma un defecto y no falló en V1); conserva el resultado de la ejecución de V1</t>
         </is>
       </c>
     </row>
@@ -2876,19 +2864,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G53" s="4" t="inlineStr">
-        <is>
-          <t>Incluido</t>
-        </is>
-      </c>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>Excluido</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr"/>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>módulo que V2 toca: Cuotas (V2 suma la compra en cuotas empezada y la confirmación destructiva)</t>
+          <t>prioridad Baja en el módulo Cuotas, que V2 toca: ninguna otra regla la incluye (no es Alta, no confirma un defecto y no falló en V1); conserva el resultado de la ejecución de V1</t>
         </is>
       </c>
     </row>
@@ -3393,19 +3377,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G64" s="4" t="inlineStr">
-        <is>
-          <t>Incluido</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>Excluido</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr"/>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>módulo que V2 toca: Monedas (las suscripciones y las deudas en USD usan el tipo de cambio)</t>
+          <t>prioridad Baja en el módulo Monedas, que V2 toca: ninguna otra regla la incluye (no es Alta, no confirma un defecto y no falló en V1); conserva el resultado de la ejecución de V1</t>
         </is>
       </c>
     </row>
@@ -3769,19 +3749,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G72" s="4" t="inlineStr">
-        <is>
-          <t>Incluido</t>
-        </is>
-      </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>Excluido</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr"/>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>módulo que V2 toca: Resumen (V2 suma el neto de reembolsos, la torta y el detalle de categoría)</t>
+          <t>prioridad Baja en el módulo Resumen, que V2 toca: ninguna otra regla la incluye (no es Alta, no confirma un defecto y no falló en V1); conserva el resultado de la ejecución de V1</t>
         </is>
       </c>
     </row>
@@ -3863,19 +3839,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G74" s="4" t="inlineStr">
-        <is>
-          <t>Incluido</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>Excluido</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr"/>
       <c r="I74" s="3" t="inlineStr">
         <is>
-          <t>módulo que V2 toca: Resumen (V2 suma el neto de reembolsos, la torta y el detalle de categoría)</t>
+          <t>prioridad Baja en el módulo Resumen, que V2 toca: ninguna otra regla la incluye (no es Alta, no confirma un defecto y no falló en V1); conserva el resultado de la ejecución de V1</t>
         </is>
       </c>
     </row>

--- a/entrega-2/03-seleccion-regresion.xlsx
+++ b/entrega-2/03-seleccion-regresion.xlsx
@@ -34,7 +34,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -54,6 +54,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE7E6E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -83,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -96,6 +101,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3956,7 +3964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3965,6 +3973,7 @@
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="90" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4002,7 +4011,12 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Resultado de la confirmación</t>
+          <t>Resultado de la confirmación (2026-10-28)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Evidencia</t>
         </is>
       </c>
     </row>
@@ -4032,9 +4046,14 @@
           <t>CP-ACC-004</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Confirmado</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Contra Supabase Auth local: crear una cuenta con «abc1234» y con «abcdefgh» responde HTTP 422 (weak_password) en las dos.</t>
         </is>
       </c>
     </row>
@@ -4064,9 +4083,14 @@
           <t>CP-CFG-004</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Confirmado</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>El movimiento muestra: «Entretenimiento archivada Efectivo -$8.000,00»</t>
         </is>
       </c>
     </row>
@@ -4096,9 +4120,14 @@
           <t>CP-REG-012</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Confirmado</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Activos tras eliminar: 0. En «Eliminados» se ve «Martes 20 de octubre Indumentaria eliminada Efectivo -$50.000,00» con botón «Restaurar»</t>
         </is>
       </c>
     </row>
@@ -4128,9 +4157,14 @@
           <t>CP-ACC-002</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Confirmado</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Sin sesión redirige a /login?next=%2Fdashboard%3Fperiod%3D2026-06; después de entrar termina en /dashboard?period=2026-06</t>
         </is>
       </c>
     </row>
@@ -4160,9 +4194,14 @@
           <t>CP-CUO-003</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Confirmado</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Con una compra en 3 cuotas, cambiar la cuenta «Tarjeta de crédito» a efectivo por API responde HTTP 400 (I6: la cuenta tiene compras en cuotas, no puede dejar de ser tarjeta de crédito) y la cuenta sigue siendo tarjeta de crédito.</t>
         </is>
       </c>
     </row>
@@ -4192,9 +4231,14 @@
           <t>Repetir los pasos del reporte (sin caso propio)</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Confirmado</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Tras archivar las 8 y abrir Registrar (dos veces): 0 categorías activas, 8 en total</t>
         </is>
       </c>
     </row>
@@ -4224,9 +4268,14 @@
           <t>CP-CFG-006</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Confirmado</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>La lista de cuentas tiene 5 botones «Editar» y 5 «Archivar» (una por cuenta)</t>
         </is>
       </c>
     </row>
@@ -4256,9 +4305,14 @@
           <t>CP-REG-010</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Confirmado</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Con 1.000.000.000.000 «Siguiente» queda deshabilitado y aparece el aviso «El monto máximo es $999.999.999.999,99».</t>
         </is>
       </c>
     </row>
@@ -4288,9 +4342,14 @@
           <t>CP-REG-011</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Confirmado</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Con US$0,01 a tipo de cambio 0,01 «Siguiente» queda deshabilitado y se ve «En pesos daría menos de $0,01.».</t>
         </is>
       </c>
     </row>
@@ -4320,9 +4379,14 @@
           <t>CP-DAS-003</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Confirmado</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Con ?period=0000-01 no hay error; la dirección pasa a /dashboard?period=2026-10 y el mes es Octubre 2026</t>
         </is>
       </c>
     </row>
@@ -4352,9 +4416,14 @@
           <t>Repetir los pasos del reporte (sin caso propio)</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Confirmado</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>10 botones de color con data-testid; 8 botones «Editar» con identificador distinto en cada fila</t>
         </is>
       </c>
     </row>
@@ -4384,9 +4453,14 @@
           <t>Repetir los pasos del reporte (sin caso propio)</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Confirmado</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Gasto de $1.000 con deuda de $400: HTTP 200 (se crea). Con deuda de $1.500: HTTP 400 I7: la deuda no puede superar el monto del gasto</t>
         </is>
       </c>
     </row>
@@ -4416,9 +4490,14 @@
           <t>CP-CFG-010</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Confirmado</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Con tipo de cambio 1250,55555 «Siguiente» queda deshabilitado y se ve «Usá hasta 4 decimales».</t>
         </is>
       </c>
     </row>
@@ -4448,9 +4527,14 @@
           <t>CP-CFG-003</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Confirmado</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Crear «salud» con «Salud» activa: «Ya existe una categoría activa con ese nombre»; en la lista queda una sola</t>
         </is>
       </c>
     </row>
@@ -4480,9 +4564,14 @@
           <t>CP-MON-003</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Confirmado</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>El tipo de cambio sugerido se muestra como «1.250,00»</t>
         </is>
       </c>
     </row>
@@ -4512,9 +4601,14 @@
           <t>Repetir los pasos del reporte (sin caso propio)</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Confirmado</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>En Chromium a 390 px de ancho, los montos entran en su casillero ($2.165.003.118,50, $81.818.491.500,00 y $79.653.488.381,50) y no hay scroll horizontal. No se probó en un iPhone con Safari.</t>
         </is>
       </c>
     </row>
@@ -4544,9 +4638,14 @@
           <t>Repetir los pasos del reporte (sin caso propio)</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>No concluyente</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Chromium: 8 de 8 altas llegan a la configuración inicial; WebKit: 8 de 8 altas llegan a la configuración inicial. El defecto era intermitente (2 de 12 en producción con WebKit, 1 de ~80 en local): 16 altas sin fallas no alcanzan para descartarlo</t>
         </is>
       </c>
     </row>
@@ -4576,9 +4675,14 @@
           <t>Repetir los pasos del reporte (sin caso propio)</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Confirmado</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>El foco entra al diálogo (true), 6 Tab seguidos no salen de él (true), Escape lo cierra (true) y el foco queda en «settings-accounts-delete»</t>
         </is>
       </c>
     </row>
@@ -4608,9 +4712,14 @@
           <t>CP-CFG-003</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Confirmado</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>El aviso «Esta cuenta tiene compras en cuotas: tiene que seguir siendo tarjeta de crédito» aparece junto a la fila que se edita (a 100 px; pantalla de 812 px)</t>
         </is>
       </c>
     </row>
@@ -4640,9 +4749,14 @@
           <t>Repetir los pasos del reporte (sin caso propio)</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Confirmado</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Con las 8 categorías archivadas, Registrar dice «No tenés categorías activas. Creá una o reactivá una archivada en Ajustes.» con enlace a Ajustes, y Ajustes muestra «Archivadas» con un botón para reactivar cada una (8). No se revisó el paso «Tus categorías» de la configuración inicial.</t>
         </is>
       </c>
     </row>
@@ -4672,9 +4786,14 @@
           <t>Repetir los pasos del reporte (sin caso propio)</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Confirmado</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Con un 429 simulado la pantalla dice: «Demasiados intentos. Esperá unos minutos antes de volver a intentar»</t>
         </is>
       </c>
     </row>
@@ -4704,9 +4823,14 @@
           <t>Repetir los pasos del reporte (sin caso propio)</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Confirmado</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Con la siembra demorada (cuentas 4 s, categorías 1,5 s) Registrar muestra 5 cuentas</t>
         </is>
       </c>
     </row>

--- a/entrega-2/03-seleccion-regresion.xlsx
+++ b/entrega-2/03-seleccion-regresion.xlsx
@@ -4640,12 +4640,12 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>No concluyente</t>
+          <t>No concluyente (cerrado por decisión del equipo)</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Chromium: 8 de 8 altas llegan a la configuración inicial; WebKit: 8 de 8 altas llegan a la configuración inicial. El defecto era intermitente (2 de 12 en producción con WebKit, 1 de ~80 en local): 16 altas sin fallas no alcanzan para descartarlo</t>
+          <t>Chromium: 8 de 8 altas llegan a la configuración inicial; WebKit: 8 de 8 altas llegan a la configuración inicial. El defecto era intermitente (2 de 12 en producción con WebKit, 1 de ~80 en local): 16 altas sin fallas no alcanzan para descartarlo El equipo decidió cerrarlo igual; se reabre si reaparece.</t>
         </is>
       </c>
     </row>

--- a/entrega-2/03-seleccion-regresion.xlsx
+++ b/entrega-2/03-seleccion-regresion.xlsx
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I76"/>
+  <dimension ref="A1:J76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -483,6 +483,7 @@
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="70" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -538,6 +539,11 @@
           <t>Motivo</t>
         </is>
       </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Resultado en V2 (regresión 2026-10-28)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -585,6 +591,11 @@
           <t>prioridad Alta</t>
         </is>
       </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -632,6 +643,11 @@
           <t>prioridad Alta; confirma DEF-008 (corregido, falta confirmación)</t>
         </is>
       </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -679,6 +695,11 @@
           <t>prioridad Alta</t>
         </is>
       </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -726,6 +747,11 @@
           <t>prioridad Alta; confirma DEF-005 (corregido, falta confirmación); falló en V1</t>
         </is>
       </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -773,6 +799,11 @@
           <t>prioridad Alta</t>
         </is>
       </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -816,6 +847,11 @@
           <t>prioridad Media en el módulo Acceso, que V2 no toca; conserva el resultado de la ejecución de V1</t>
         </is>
       </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>— (excluido: conserva el resultado de V1)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -859,6 +895,11 @@
           <t>prioridad Media en el módulo Acceso, que V2 no toca; conserva el resultado de la ejecución de V1</t>
         </is>
       </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>— (excluido: conserva el resultado de V1)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -906,6 +947,11 @@
           <t>prioridad Alta</t>
         </is>
       </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -953,6 +999,11 @@
           <t>prioridad Alta</t>
         </is>
       </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -996,6 +1047,11 @@
           <t>prioridad Media en el módulo Acceso, que V2 no toca; conserva el resultado de la ejecución de V1</t>
         </is>
       </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>— (excluido: conserva el resultado de V1)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -1043,6 +1099,11 @@
           <t>prioridad Alta</t>
         </is>
       </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -1090,6 +1151,11 @@
           <t>prioridad Alta</t>
         </is>
       </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -1137,6 +1203,11 @@
           <t>prioridad Alta</t>
         </is>
       </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -1180,6 +1251,11 @@
           <t>prioridad Media en el módulo Configuración, que V2 no toca; conserva el resultado de la ejecución de V1</t>
         </is>
       </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>— (excluido: conserva el resultado de V1)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -1227,6 +1303,11 @@
           <t>confirma DEF-019 y DEF-025 (corregido, falta confirmación)</t>
         </is>
       </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -1274,6 +1355,11 @@
           <t>prioridad Alta; confirma DEF-006 (corregido, falta confirmación); falló en V1</t>
         </is>
       </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -1308,13 +1394,22 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Excluido</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr"/>
+          <t>Incluido</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>prioridad Baja en el módulo Configuración, que V2 no toca; conserva el resultado de la ejecución de V1</t>
+          <t>sumado el 2026-10-28 (§6): ejercita la unicidad de nombres de categoría, que cambió con DEF-019 (sin distinguir mayúsculas)</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -1364,6 +1459,11 @@
           <t>prioridad Alta; V2 lo usa: cuentas de Ajustes (las usan suscripciones y registro); confirma DEF-011 (corregido, falta confirmación)</t>
         </is>
       </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -1411,6 +1511,11 @@
           <t>V2 lo usa: cuentas de Ajustes (las usan suscripciones y registro)</t>
         </is>
       </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -1458,6 +1563,11 @@
           <t>prioridad Alta</t>
         </is>
       </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -1505,6 +1615,11 @@
           <t>prioridad Alta; V2 lo usa: tipo de cambio de referencia (lo usan suscripciones y deudas en USD)</t>
         </is>
       </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -1552,6 +1667,11 @@
           <t>V2 lo usa: tipo de cambio de referencia (lo usan suscripciones y deudas en USD); confirma DEF-018 (corregido, falta confirmación)</t>
         </is>
       </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -1599,6 +1719,11 @@
           <t>prioridad Alta</t>
         </is>
       </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -1642,6 +1767,11 @@
           <t>prioridad Media en el módulo Configuración, que V2 no toca; conserva el resultado de la ejecución de V1</t>
         </is>
       </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>— (excluido: conserva el resultado de V1)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -1676,13 +1806,22 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Excluido</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr"/>
+          <t>Incluido</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>prioridad Media en el módulo Configuración, que V2 no toca; conserva el resultado de la ejecución de V1</t>
+          <t>sumado el 2026-10-28 (§6): el paso «Tus categorías» de la configuración inicial cambió con DEF-026</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -1728,6 +1867,11 @@
           <t>prioridad Media en el módulo Configuración, que V2 no toca; conserva el resultado de la ejecución de V1</t>
         </is>
       </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>— (excluido: conserva el resultado de V1)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -1771,6 +1915,11 @@
           <t>prioridad Baja en el módulo Configuración, que V2 no toca; conserva el resultado de la ejecución de V1</t>
         </is>
       </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>— (excluido: conserva el resultado de V1)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -1818,6 +1967,11 @@
           <t>prioridad Alta; módulo que V2 toca: Registro (V2 suma gasto compartido, aviso de guardado y confirmación de borrado)</t>
         </is>
       </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -1865,6 +2019,11 @@
           <t>módulo que V2 toca: Registro (V2 suma gasto compartido, aviso de guardado y confirmación de borrado)</t>
         </is>
       </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -1908,6 +2067,11 @@
           <t>prioridad Baja en el módulo Registro, que V2 toca: ninguna otra regla la incluye (no es Alta, no confirma un defecto y no falló en V1); conserva el resultado de la ejecución de V1</t>
         </is>
       </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>— (excluido: conserva el resultado de V1)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -1955,6 +2119,11 @@
           <t>módulo que V2 toca: Registro (V2 suma gasto compartido, aviso de guardado y confirmación de borrado)</t>
         </is>
       </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -2002,6 +2171,11 @@
           <t>módulo que V2 toca: Registro (V2 suma gasto compartido, aviso de guardado y confirmación de borrado)</t>
         </is>
       </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -2045,6 +2219,11 @@
           <t>prioridad Baja en el módulo Registro, que V2 toca: ninguna otra regla la incluye (no es Alta, no confirma un defecto y no falló en V1); conserva el resultado de la ejecución de V1</t>
         </is>
       </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>— (excluido: conserva el resultado de V1)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -2088,6 +2267,11 @@
           <t>prioridad Baja en el módulo Registro, que V2 toca: ninguna otra regla la incluye (no es Alta, no confirma un defecto y no falló en V1); conserva el resultado de la ejecución de V1</t>
         </is>
       </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>— (excluido: conserva el resultado de V1)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -2135,6 +2319,11 @@
           <t>módulo que V2 toca: Registro (V2 suma gasto compartido, aviso de guardado y confirmación de borrado)</t>
         </is>
       </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -2182,6 +2371,11 @@
           <t>módulo que V2 toca: Registro (V2 suma gasto compartido, aviso de guardado y confirmación de borrado)</t>
         </is>
       </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -2229,6 +2423,11 @@
           <t>prioridad Alta; módulo que V2 toca: Registro (V2 suma gasto compartido, aviso de guardado y confirmación de borrado); confirma DEF-012 (corregido, falta confirmación)</t>
         </is>
       </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -2276,6 +2475,11 @@
           <t>módulo que V2 toca: Registro (V2 suma gasto compartido, aviso de guardado y confirmación de borrado); confirma DEF-013 (corregido, falta confirmación)</t>
         </is>
       </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -2323,6 +2527,11 @@
           <t>prioridad Alta; módulo que V2 toca: Registro (V2 suma gasto compartido, aviso de guardado y confirmación de borrado); confirma DEF-007 (corregido, falta confirmación)</t>
         </is>
       </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -2370,6 +2579,11 @@
           <t>prioridad Alta; módulo que V2 toca: Registro (V2 suma gasto compartido, aviso de guardado y confirmación de borrado)</t>
         </is>
       </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -2417,6 +2631,11 @@
           <t>prioridad Alta; módulo que V2 toca: Registro (V2 suma gasto compartido, aviso de guardado y confirmación de borrado)</t>
         </is>
       </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -2464,6 +2683,11 @@
           <t>prioridad Alta; módulo que V2 toca: Registro (V2 suma gasto compartido, aviso de guardado y confirmación de borrado)</t>
         </is>
       </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -2511,6 +2735,11 @@
           <t>módulo que V2 toca: Registro (V2 suma gasto compartido, aviso de guardado y confirmación de borrado)</t>
         </is>
       </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -2558,6 +2787,11 @@
           <t>prioridad Alta; módulo que V2 toca: Cuotas (V2 suma la compra en cuotas empezada y la confirmación destructiva)</t>
         </is>
       </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -2605,6 +2839,11 @@
           <t>prioridad Alta; módulo que V2 toca: Cuotas (V2 suma la compra en cuotas empezada y la confirmación destructiva)</t>
         </is>
       </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -2652,6 +2891,11 @@
           <t>prioridad Alta; módulo que V2 toca: Cuotas (V2 suma la compra en cuotas empezada y la confirmación destructiva); confirma DEF-009 (corregido, falta confirmación)</t>
         </is>
       </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
@@ -2699,6 +2943,11 @@
           <t>prioridad Alta; módulo que V2 toca: Cuotas (V2 suma la compra en cuotas empezada y la confirmación destructiva)</t>
         </is>
       </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
@@ -2746,6 +2995,11 @@
           <t>prioridad Alta; módulo que V2 toca: Cuotas (V2 suma la compra en cuotas empezada y la confirmación destructiva)</t>
         </is>
       </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -2793,6 +3047,11 @@
           <t>prioridad Alta; módulo que V2 toca: Cuotas (V2 suma la compra en cuotas empezada y la confirmación destructiva)</t>
         </is>
       </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
@@ -2840,6 +3099,11 @@
           <t>módulo que V2 toca: Cuotas (V2 suma la compra en cuotas empezada y la confirmación destructiva)</t>
         </is>
       </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -2883,6 +3147,11 @@
           <t>prioridad Baja en el módulo Cuotas, que V2 toca: ninguna otra regla la incluye (no es Alta, no confirma un defecto y no falló en V1); conserva el resultado de la ejecución de V1</t>
         </is>
       </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>— (excluido: conserva el resultado de V1)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
@@ -2930,6 +3199,11 @@
           <t>prioridad Alta; módulo que V2 toca: Cuotas (V2 suma la compra en cuotas empezada y la confirmación destructiva)</t>
         </is>
       </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -2977,6 +3251,11 @@
           <t>módulo que V2 toca: Cuotas (V2 suma la compra en cuotas empezada y la confirmación destructiva)</t>
         </is>
       </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
@@ -3024,6 +3303,11 @@
           <t>prioridad Alta; módulo que V2 toca: Cuotas (V2 suma la compra en cuotas empezada y la confirmación destructiva)</t>
         </is>
       </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
@@ -3071,6 +3355,11 @@
           <t>prioridad Alta; módulo que V2 toca: Cuotas (V2 suma la compra en cuotas empezada y la confirmación destructiva)</t>
         </is>
       </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
@@ -3118,6 +3407,11 @@
           <t>prioridad Alta; módulo que V2 toca: Cuotas (V2 suma la compra en cuotas empezada y la confirmación destructiva)</t>
         </is>
       </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -3165,6 +3459,11 @@
           <t>prioridad Alta; módulo que V2 toca: Monedas (las suscripciones y las deudas en USD usan el tipo de cambio)</t>
         </is>
       </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
@@ -3212,6 +3511,11 @@
           <t>prioridad Alta; módulo que V2 toca: Monedas (las suscripciones y las deudas en USD usan el tipo de cambio)</t>
         </is>
       </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -3259,6 +3563,11 @@
           <t>módulo que V2 toca: Monedas (las suscripciones y las deudas en USD usan el tipo de cambio); confirma DEF-020 (corregido, falta confirmación)</t>
         </is>
       </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
@@ -3306,6 +3615,11 @@
           <t>prioridad Alta; módulo que V2 toca: Monedas (las suscripciones y las deudas en USD usan el tipo de cambio)</t>
         </is>
       </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
@@ -3353,6 +3667,11 @@
           <t>prioridad Alta; módulo que V2 toca: Monedas (las suscripciones y las deudas en USD usan el tipo de cambio)</t>
         </is>
       </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
@@ -3396,6 +3715,11 @@
           <t>prioridad Baja en el módulo Monedas, que V2 toca: ninguna otra regla la incluye (no es Alta, no confirma un defecto y no falló en V1); conserva el resultado de la ejecución de V1</t>
         </is>
       </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>— (excluido: conserva el resultado de V1)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -3443,6 +3767,11 @@
           <t>prioridad Alta; módulo que V2 toca: Monedas (las suscripciones y las deudas en USD usan el tipo de cambio)</t>
         </is>
       </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
@@ -3490,6 +3819,11 @@
           <t>prioridad Alta; módulo que V2 toca: Resumen (V2 suma el neto de reembolsos, la torta y el detalle de categoría)</t>
         </is>
       </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
@@ -3537,6 +3871,11 @@
           <t>prioridad Alta; módulo que V2 toca: Resumen (V2 suma el neto de reembolsos, la torta y el detalle de categoría)</t>
         </is>
       </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
@@ -3584,6 +3923,11 @@
           <t>módulo que V2 toca: Resumen (V2 suma el neto de reembolsos, la torta y el detalle de categoría); confirma DEF-014 (corregido, falta confirmación)</t>
         </is>
       </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -3631,6 +3975,11 @@
           <t>módulo que V2 toca: Resumen (V2 suma el neto de reembolsos, la torta y el detalle de categoría)</t>
         </is>
       </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
@@ -3678,6 +4027,11 @@
           <t>módulo que V2 toca: Resumen (V2 suma el neto de reembolsos, la torta y el detalle de categoría)</t>
         </is>
       </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
@@ -3725,6 +4079,11 @@
           <t>módulo que V2 toca: Resumen (V2 suma el neto de reembolsos, la torta y el detalle de categoría)</t>
         </is>
       </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
@@ -3768,6 +4127,11 @@
           <t>prioridad Baja en el módulo Resumen, que V2 toca: ninguna otra regla la incluye (no es Alta, no confirma un defecto y no falló en V1); conserva el resultado de la ejecución de V1</t>
         </is>
       </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>— (excluido: conserva el resultado de V1)</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -3815,6 +4179,11 @@
           <t>módulo que V2 toca: Resumen (V2 suma el neto de reembolsos, la torta y el detalle de categoría)</t>
         </is>
       </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
@@ -3858,6 +4227,11 @@
           <t>prioridad Baja en el módulo Resumen, que V2 toca: ninguna otra regla la incluye (no es Alta, no confirma un defecto y no falló en V1); conserva el resultado de la ejecución de V1</t>
         </is>
       </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>— (excluido: conserva el resultado de V1)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
@@ -3905,6 +4279,11 @@
           <t>módulo que V2 toca: Resumen (V2 suma el neto de reembolsos, la torta y el detalle de categoría)</t>
         </is>
       </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
@@ -3950,6 +4329,11 @@
       <c r="I76" s="3" t="inlineStr">
         <is>
           <t>prioridad Alta; módulo que V2 toca: Resumen (V2 suma el neto de reembolsos, la torta y el detalle de categoría)</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -4053,7 +4437,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Contra Supabase Auth local: crear una cuenta con «abc1234» y con «abcdefgh» responde HTTP 422 (weak_password) en las dos.</t>
+          <t>Contra Supabase Auth local con la configuración del repositorio (8 caracteres, mayúscula, minúscula, número y símbolo): «abc1234», «abcdefgh» y «abcd1234» responden HTTP 422 (weak_password); «Abcd123!» crea la cuenta. Repetido el 2026-10-28 después de reiniciar Supabase local, que estaba levantado con una configuración vieja de Auth (ver `06`, §6, regresión). En el proyecto hosteado no se verificó.</t>
         </is>
       </c>
     </row>
@@ -4603,12 +4987,12 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Confirmado</t>
+          <t>Confirmado parcial</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>En Chromium a 390 px de ancho, los montos entran en su casillero ($2.165.003.118,50, $81.818.491.500,00 y $79.653.488.381,50) y no hay scroll horizontal. No se probó en un iPhone con Safari.</t>
+          <t>En WebKit (el motor de Safari) con el viewport de iPhone 13 (390 px), los montos entran en su casillero ($2.165.003.118,00, $81.818.491.500,00 y $79.653.488.382,00), el porcentaje no baja de línea y no hay scroll horizontal; antes, igual en Chromium a 390 px. Falta probarlo en un iPhone real.</t>
         </is>
       </c>
     </row>
@@ -4756,7 +5140,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Con las 8 categorías archivadas, Registrar dice «No tenés categorías activas. Creá una o reactivá una archivada en Ajustes.» con enlace a Ajustes, y Ajustes muestra «Archivadas» con un botón para reactivar cada una (8). No se revisó el paso «Tus categorías» de la configuración inicial.</t>
+          <t>Con las 8 categorías archivadas, Registrar dice «No tenés categorías activas. Creá una o reactivá una archivada en Ajustes.» con enlace a Ajustes, y Ajustes muestra «Archivadas» con un botón para reactivar cada una (8). Al reabrir la configuración inicial, «Tus categorías» dice «No tenés categorías activas. Cuando termines, podés crearlas o reactivar las archivadas desde Ajustes.» y deja continuar, y «Registrá tu primer gasto» muestra el aviso con enlace a Ajustes y deja saltear (completado el 2026-10-28).</t>
         </is>
       </c>
     </row>
@@ -4788,12 +5172,12 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Confirmado</t>
+          <t>Confirmado parcial</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Con un 429 simulado la pantalla dice: «Demasiados intentos. Esperá unos minutos antes de volver a intentar»</t>
+          <t>Con un 429 simulado (respuesta interceptada) la pantalla dice: «Demasiados intentos. Esperá unos minutos antes de volver a intentar». No se llegó al límite real de altas.</t>
         </is>
       </c>
     </row>
@@ -4825,12 +5209,12 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Confirmado</t>
+          <t>Confirmado parcial</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Con la siembra demorada (cuentas 4 s, categorías 1,5 s) Registrar muestra 5 cuentas</t>
+          <t>Con la siembra demorada a propósito (cuentas 4 s, categorías 1,5 s) Registrar muestra 5 cuentas. No se reprodujo una demora real.</t>
         </is>
       </c>
     </row>
